--- a/assets/constructions/examples/ctd_tsmb_tupleback_boring.xlsx
+++ b/assets/constructions/examples/ctd_tsmb_tupleback_boring.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN3"/>
+  <dimension ref="A1:AS3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -627,6 +627,31 @@
       <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>releasepack</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
         </is>
       </c>
     </row>
@@ -743,6 +768,17 @@
           <t>Groovex Main Catalog EE 2019 WEB</t>
         </is>
       </c>
+      <c r="AO2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -857,6 +893,17 @@
           <t>Groovex Main Catalog EE 2019 WEB</t>
         </is>
       </c>
+      <c r="AO3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
